--- a/data/mesquite_proximity_fall2026.xlsx
+++ b/data/mesquite_proximity_fall2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fernbromley/Desktop/AVCA_BANWR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB154ABF-110A-C345-A904-BC76CC853E8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A18D012F-2EA8-0B4A-A948-3EDE3E9EF1AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="680" yWindow="660" windowWidth="28040" windowHeight="17160" xr2:uid="{B862D82C-49C1-F543-9C47-75B7F00BA096}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>plot</t>
   </si>
@@ -48,6 +48,81 @@
   </si>
   <si>
     <t>direction</t>
+  </si>
+  <si>
+    <t>C23</t>
+  </si>
+  <si>
+    <t>C5</t>
+  </si>
+  <si>
+    <t>C36</t>
+  </si>
+  <si>
+    <t>C26</t>
+  </si>
+  <si>
+    <t>C48</t>
+  </si>
+  <si>
+    <t>C24</t>
+  </si>
+  <si>
+    <t>C28</t>
+  </si>
+  <si>
+    <t>C22</t>
+  </si>
+  <si>
+    <t>C18</t>
+  </si>
+  <si>
+    <t>C34</t>
+  </si>
+  <si>
+    <t>C33</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>C49</t>
+  </si>
+  <si>
+    <t>C40</t>
+  </si>
+  <si>
+    <t>C27</t>
+  </si>
+  <si>
+    <t>C14</t>
+  </si>
+  <si>
+    <t>C21</t>
+  </si>
+  <si>
+    <t>C43</t>
+  </si>
+  <si>
+    <t>C7</t>
+  </si>
+  <si>
+    <t>C16</t>
+  </si>
+  <si>
+    <t>C50</t>
+  </si>
+  <si>
+    <t>C44</t>
+  </si>
+  <si>
+    <t>C25</t>
+  </si>
+  <si>
+    <t>C32</t>
   </si>
 </sst>
 </file>
@@ -419,7 +494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFF12CE4-99FC-884B-8386-7E80CE8B8E93}">
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -972,6 +1047,281 @@
         <v>109</v>
       </c>
     </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>3</v>
+      </c>
+      <c r="B51">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C51">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>4</v>
+      </c>
+      <c r="B52">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C52">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>5</v>
+      </c>
+      <c r="B53">
+        <v>2.9</v>
+      </c>
+      <c r="C53">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>6</v>
+      </c>
+      <c r="B54">
+        <v>14.5</v>
+      </c>
+      <c r="C54">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55">
+        <v>3.5</v>
+      </c>
+      <c r="C55">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>8</v>
+      </c>
+      <c r="B56">
+        <v>1.5</v>
+      </c>
+      <c r="C56">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>10</v>
+      </c>
+      <c r="B57">
+        <v>1.7</v>
+      </c>
+      <c r="C57">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>11</v>
+      </c>
+      <c r="B58">
+        <v>3.9</v>
+      </c>
+      <c r="C58">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>12</v>
+      </c>
+      <c r="B59">
+        <v>2</v>
+      </c>
+      <c r="C59">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>13</v>
+      </c>
+      <c r="B60">
+        <v>4</v>
+      </c>
+      <c r="C60">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>14</v>
+      </c>
+      <c r="B61">
+        <v>4.8</v>
+      </c>
+      <c r="C61">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62">
+        <v>1.05</v>
+      </c>
+      <c r="C62">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>16</v>
+      </c>
+      <c r="B63">
+        <v>5.3</v>
+      </c>
+      <c r="C63">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>17</v>
+      </c>
+      <c r="B64">
+        <v>3.4</v>
+      </c>
+      <c r="C64">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>18</v>
+      </c>
+      <c r="B65">
+        <v>3.4</v>
+      </c>
+      <c r="C65">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>19</v>
+      </c>
+      <c r="B66">
+        <v>1.7</v>
+      </c>
+      <c r="C66">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>9</v>
+      </c>
+      <c r="B67">
+        <v>2.9</v>
+      </c>
+      <c r="C67">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>20</v>
+      </c>
+      <c r="B68">
+        <v>5.3</v>
+      </c>
+      <c r="C68">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>21</v>
+      </c>
+      <c r="B69">
+        <v>2.5</v>
+      </c>
+      <c r="C69">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>22</v>
+      </c>
+      <c r="B70">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C70">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>23</v>
+      </c>
+      <c r="B71">
+        <v>1.9</v>
+      </c>
+      <c r="C71">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>24</v>
+      </c>
+      <c r="B72">
+        <v>2.4</v>
+      </c>
+      <c r="C72">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>25</v>
+      </c>
+      <c r="B73">
+        <v>1.8</v>
+      </c>
+      <c r="C73">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>26</v>
+      </c>
+      <c r="B74">
+        <v>1.3</v>
+      </c>
+      <c r="C74">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>27</v>
+      </c>
+      <c r="B75">
+        <v>3.4</v>
+      </c>
+      <c r="C75">
+        <v>180</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/mesquite_proximity_fall2026.xlsx
+++ b/data/mesquite_proximity_fall2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fernbromley/Desktop/AVCA_BANWR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A18D012F-2EA8-0B4A-A948-3EDE3E9EF1AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21DEC3A6-B814-1041-9D16-19F820D97FCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="680" yWindow="660" windowWidth="28040" windowHeight="17160" xr2:uid="{B862D82C-49C1-F543-9C47-75B7F00BA096}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>plot</t>
   </si>
@@ -123,6 +123,18 @@
   </si>
   <si>
     <t>C32</t>
+  </si>
+  <si>
+    <t>C47</t>
+  </si>
+  <si>
+    <t>C37</t>
+  </si>
+  <si>
+    <t>C15</t>
+  </si>
+  <si>
+    <t>C41</t>
   </si>
 </sst>
 </file>
@@ -494,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFF12CE4-99FC-884B-8386-7E80CE8B8E93}">
-  <dimension ref="A1:C75"/>
+  <dimension ref="A1:C79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -1322,6 +1334,50 @@
         <v>180</v>
       </c>
     </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>28</v>
+      </c>
+      <c r="B76">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C76">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>29</v>
+      </c>
+      <c r="B77">
+        <v>4.5</v>
+      </c>
+      <c r="C77">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>30</v>
+      </c>
+      <c r="B78">
+        <v>5</v>
+      </c>
+      <c r="C78">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>31</v>
+      </c>
+      <c r="B79">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C79">
+        <v>47</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
